--- a/incentive-tracking/data/new_belgium_distribution_retain.xlsx
+++ b/incentive-tracking/data/new_belgium_distribution_retain.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="220">
   <si>
     <t>Placements</t>
   </si>
@@ -26,21 +26,24 @@
     <t/>
   </si>
   <si>
+    <t>58.1%</t>
+  </si>
+  <si>
     <t>26.7%</t>
   </si>
   <si>
     <t>30.0%</t>
   </si>
   <si>
-    <t>47.6%</t>
-  </si>
-  <si>
     <t>46.2%</t>
   </si>
   <si>
     <t>Shane Barreca</t>
   </si>
   <si>
+    <t>73.6%</t>
+  </si>
+  <si>
     <t>NonZero</t>
   </si>
   <si>
@@ -80,16 +83,22 @@
     <t>51.7%</t>
   </si>
   <si>
+    <t>79.4%</t>
+  </si>
+  <si>
     <t>16.7%</t>
   </si>
   <si>
+    <t>72.2%</t>
+  </si>
+  <si>
     <t>55.6%</t>
   </si>
   <si>
     <t>28.6%</t>
   </si>
   <si>
-    <t>64.6%</t>
+    <t>60.7%</t>
   </si>
   <si>
     <t>Report Version</t>
@@ -107,9 +116,6 @@
     <t>Anthony Palmisano</t>
   </si>
   <si>
-    <t>57.5%</t>
-  </si>
-  <si>
     <t>10702 Bell's Two Hearted 2/12/12 oz Can</t>
   </si>
   <si>
@@ -128,6 +134,9 @@
     <t>57.1%</t>
   </si>
   <si>
+    <t>58.9%</t>
+  </si>
+  <si>
     <t>14.3%</t>
   </si>
   <si>
@@ -167,9 +176,6 @@
     <t>Derrick Laws</t>
   </si>
   <si>
-    <t>32.7%</t>
-  </si>
-  <si>
     <t>41.7%</t>
   </si>
   <si>
@@ -194,12 +200,6 @@
     <t>LoadSheet Status</t>
   </si>
   <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>85.0%</t>
-  </si>
-  <si>
     <t>20207 Kirin Ichiban 1/15/19.2 oz Can</t>
   </si>
   <si>
@@ -209,25 +209,22 @@
     <t>150.0%</t>
   </si>
   <si>
-    <t>64.5%</t>
-  </si>
-  <si>
-    <t>56.9%</t>
+    <t>38.5%</t>
   </si>
   <si>
     <t>77.8%</t>
   </si>
   <si>
-    <t>38.5%</t>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>111.1%</t>
   </si>
   <si>
     <t>76.0%</t>
   </si>
   <si>
-    <t>58.0%</t>
-  </si>
-  <si>
-    <t>51.2%</t>
+    <t>70.6%</t>
   </si>
   <si>
     <t>Sales Route Num</t>
@@ -245,22 +242,22 @@
     <t>10701 Bell's Two Hearted 4/6/12 oz Btl</t>
   </si>
   <si>
-    <t>84.0%</t>
-  </si>
-  <si>
-    <t>90.5%</t>
+    <t>67.8%</t>
+  </si>
+  <si>
+    <t>76.8%</t>
+  </si>
+  <si>
+    <t>37.5%</t>
+  </si>
+  <si>
+    <t>200%</t>
   </si>
   <si>
     <t>10704 Bell's Two Hearted 1/15/19.2 oz Can</t>
   </si>
   <si>
-    <t>37.5%</t>
-  </si>
-  <si>
-    <t>60.6%</t>
-  </si>
-  <si>
-    <t>200%</t>
+    <t>67.4%</t>
   </si>
   <si>
     <t>Report Created Time</t>
@@ -281,27 +278,27 @@
     <t>Sales Rep Name / Package Group / Product Num Name</t>
   </si>
   <si>
-    <t>45.5%</t>
+    <t>54.5%</t>
   </si>
   <si>
     <t>6790 New Belgium Voodoo Ranger Fruit Force IPA 1/15/19.2 oz Can</t>
   </si>
   <si>
+    <t>78.3%</t>
+  </si>
+  <si>
     <t>53.1%</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>72.9%</t>
-  </si>
-  <si>
-    <t>54.5%</t>
-  </si>
-  <si>
     <t>Jim Heaney</t>
   </si>
   <si>
+    <t>58.8%</t>
+  </si>
+  <si>
     <t>65.0%</t>
   </si>
   <si>
@@ -329,7 +326,7 @@
     <t>6778 New Belgium Voodoo Ranger Juice Force IPA 1/15/19.2 oz Can</t>
   </si>
   <si>
-    <t>53.5%</t>
+    <t>65.4%</t>
   </si>
   <si>
     <t>62.5%</t>
@@ -341,7 +338,7 @@
     <t>107007 Bell's Big Hearted 1/15/19.2 oz Can</t>
   </si>
   <si>
-    <t>74.4%</t>
+    <t>47.4%</t>
   </si>
   <si>
     <t>22.2%</t>
@@ -350,6 +347,12 @@
     <t>Mike Ast</t>
   </si>
   <si>
+    <t>62.9%</t>
+  </si>
+  <si>
+    <t>52.1%</t>
+  </si>
+  <si>
     <t>116.7%</t>
   </si>
   <si>
@@ -374,33 +377,30 @@
     <t>Sales Rep Name</t>
   </si>
   <si>
-    <t>72.0%</t>
+    <t>90.0%</t>
   </si>
   <si>
     <t>20211 Kirin Light 4/6/12 oz Btl</t>
   </si>
   <si>
-    <t>64.4%</t>
-  </si>
-  <si>
     <t>20204 Kirin Ichiban 2/12/12 oz Can</t>
   </si>
   <si>
-    <t>90.0%</t>
-  </si>
-  <si>
-    <t>42.1%</t>
+    <t>74.8%</t>
   </si>
   <si>
     <t>Matt Powierski</t>
   </si>
   <si>
-    <t>60.1%</t>
+    <t>61.5%</t>
   </si>
   <si>
     <t>29.4%</t>
   </si>
   <si>
+    <t>86.7%</t>
+  </si>
+  <si>
     <t>Report Owner</t>
   </si>
   <si>
@@ -422,6 +422,12 @@
     <t>Total</t>
   </si>
   <si>
+    <t>63.0%</t>
+  </si>
+  <si>
+    <t>58.3%</t>
+  </si>
+  <si>
     <t>85.7%</t>
   </si>
   <si>
@@ -437,24 +443,12 @@
     <t>10755 Bell's Variety 2/12/12 oz Can</t>
   </si>
   <si>
-    <t>42.5%</t>
-  </si>
-  <si>
-    <t>58.3%</t>
-  </si>
-  <si>
-    <t>64.8%</t>
-  </si>
-  <si>
-    <t>52.9%</t>
+    <t>55.8%</t>
   </si>
   <si>
     <t>114.3%</t>
   </si>
   <si>
-    <t>93.3%</t>
-  </si>
-  <si>
     <t>Location</t>
   </si>
   <si>
@@ -482,6 +476,9 @@
     <t>39.3%</t>
   </si>
   <si>
+    <t>81.8%</t>
+  </si>
+  <si>
     <t>36.4%</t>
   </si>
   <si>
@@ -509,7 +506,7 @@
     <t>20201 Kirin Ichiban 4/6/12 oz Btl</t>
   </si>
   <si>
-    <t>69.6%</t>
+    <t>86.2%</t>
   </si>
   <si>
     <t>10731 Bell's Light Hearted Ale 4/6/12 oz Can</t>
@@ -521,21 +518,21 @@
     <t>83.3%</t>
   </si>
   <si>
-    <t>57.7%</t>
-  </si>
-  <si>
     <t>78.6%</t>
   </si>
   <si>
-    <t>34.0%</t>
-  </si>
-  <si>
-    <t>53.8%</t>
+    <t>38.3%</t>
+  </si>
+  <si>
+    <t>44.4%</t>
   </si>
   <si>
     <t>68.2%</t>
   </si>
   <si>
+    <t>61.0%</t>
+  </si>
+  <si>
     <t>Cache Created Time</t>
   </si>
   <si>
@@ -557,9 +554,6 @@
     <t>Dist End</t>
   </si>
   <si>
-    <t>56.7%</t>
-  </si>
-  <si>
     <t>6731 New Belgium Voodoo Ranger Imperial IPA 1/15/19.2 oz Can</t>
   </si>
   <si>
@@ -569,15 +563,12 @@
     <t>91.7%</t>
   </si>
   <si>
+    <t>52.4%</t>
+  </si>
+  <si>
     <t>89.5%</t>
   </si>
   <si>
-    <t>68.6%</t>
-  </si>
-  <si>
-    <t>64.3%</t>
-  </si>
-  <si>
     <t>73.3%</t>
   </si>
   <si>
@@ -611,13 +602,7 @@
     <t>Michael Harboy</t>
   </si>
   <si>
-    <t>58.6%</t>
-  </si>
-  <si>
-    <t>58.2%</t>
-  </si>
-  <si>
-    <t>46.7%</t>
+    <t>63.3%</t>
   </si>
   <si>
     <t>Value</t>
@@ -635,16 +620,16 @@
     <t>Product</t>
   </si>
   <si>
+    <t>87.5%</t>
+  </si>
+  <si>
     <t>88.9%</t>
   </si>
   <si>
     <t>Klejdi Lamo</t>
   </si>
   <si>
-    <t>48.2%</t>
-  </si>
-  <si>
-    <t>72.7%</t>
+    <t>53.3%</t>
   </si>
   <si>
     <t>{@Package}</t>
@@ -665,9 +650,6 @@
     <t>Chris Payton</t>
   </si>
   <si>
-    <t>62.7%</t>
-  </si>
-  <si>
     <t>40.0%</t>
   </si>
   <si>
@@ -677,7 +659,13 @@
     <t>Dave Ehlers</t>
   </si>
   <si>
-    <t>71.7%</t>
+    <t>78.9%</t>
+  </si>
+  <si>
+    <t>69.5%</t>
+  </si>
+  <si>
+    <t>65.6%</t>
   </si>
   <si>
     <t>Trade Channel</t>
@@ -980,10 +968,10 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="10">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="8">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="13">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="13">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="14">
@@ -1007,10 +995,10 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="7">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="6">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="6">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="5">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="1">
@@ -1328,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <dimension ref="A1:E273"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="55.68359375" bestFit="1" customWidth="1"/>
@@ -1339,11 +1327,11 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>191</v>
+      <c r="A1" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>188</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>0</v>
@@ -1352,7 +1340,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
@@ -1363,52 +1351,52 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>1092</v>
+        <v>1150</v>
       </c>
       <c r="D2" s="2">
         <v>1826</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D3" s="7">
         <v>160</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>30</v>
+      <c r="E3" s="5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>44</v>
+        <v>189</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C4" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="4">
         <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2</v>
@@ -1420,12 +1408,12 @@
         <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -1437,29 +1425,29 @@
         <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C7" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>2</v>
@@ -1471,15 +1459,15 @@
         <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C9" s="4">
         <v>54</v>
@@ -1488,12 +1476,12 @@
         <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>2</v>
@@ -1505,12 +1493,12 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>2</v>
@@ -1522,12 +1510,12 @@
         <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>2</v>
@@ -1539,12 +1527,12 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>2</v>
@@ -1556,12 +1544,12 @@
         <v>20</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>2</v>
@@ -1573,12 +1561,12 @@
         <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>2</v>
@@ -1590,12 +1578,12 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>2</v>
@@ -1607,15 +1595,15 @@
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
@@ -1624,12 +1612,12 @@
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>2</v>
@@ -1641,12 +1629,12 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>2</v>
@@ -1658,12 +1646,12 @@
         <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>2</v>
@@ -1675,32 +1663,32 @@
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C21" s="7">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D21" s="7">
         <v>177</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>216</v>
+      <c r="E21" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>44</v>
+        <v>189</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C22" s="4">
         <v>31</v>
@@ -1709,12 +1697,12 @@
         <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>2</v>
@@ -1726,12 +1714,12 @@
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>2</v>
@@ -1743,12 +1731,12 @@
         <v>2</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>2</v>
@@ -1760,12 +1748,12 @@
         <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>2</v>
@@ -1777,12 +1765,12 @@
         <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>2</v>
@@ -1794,12 +1782,12 @@
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>2</v>
@@ -1811,97 +1799,97 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C29" s="4">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D29" s="4">
         <v>107</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C30" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2">
         <v>10</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C31" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2">
         <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2">
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2">
         <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>164</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>2</v>
@@ -1913,29 +1901,29 @@
         <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2">
         <v>10</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>2</v>
@@ -1947,46 +1935,46 @@
         <v>10</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C37" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" s="4">
         <v>10</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>4</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="2">
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>2</v>
@@ -1998,12 +1986,12 @@
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>2</v>
@@ -2015,32 +2003,32 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D41" s="7">
         <v>104</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>121</v>
+      <c r="E41" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>44</v>
+        <v>189</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C42" s="4">
         <v>17</v>
@@ -2054,7 +2042,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>2</v>
@@ -2066,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44">
@@ -2083,12 +2071,12 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>2</v>
@@ -2105,7 +2093,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>2</v>
@@ -2117,12 +2105,12 @@
         <v>5</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>2</v>
@@ -2134,29 +2122,29 @@
         <v>5</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C48" s="4">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D48" s="4">
         <v>56</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>2</v>
@@ -2168,12 +2156,12 @@
         <v>5</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>2</v>
@@ -2185,7 +2173,7 @@
         <v>11</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -2202,12 +2190,12 @@
         <v>4</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>2</v>
@@ -2219,12 +2207,12 @@
         <v>4</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>2</v>
@@ -2241,7 +2229,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>2</v>
@@ -2253,29 +2241,29 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2">
         <v>5</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>2</v>
@@ -2292,10 +2280,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C57" s="4">
         <v>8</v>
@@ -2304,12 +2292,12 @@
         <v>16</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>2</v>
@@ -2321,12 +2309,12 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>2</v>
@@ -2338,46 +2326,46 @@
         <v>3</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D60" s="7">
         <v>155</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>92</v>
+      <c r="E60" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>44</v>
+        <v>189</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C61" s="4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D61" s="4">
         <v>43</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>2</v>
@@ -2389,12 +2377,12 @@
         <v>3</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>2</v>
@@ -2406,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -2423,12 +2411,12 @@
         <v>4</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>2</v>
@@ -2440,12 +2428,12 @@
         <v>10</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>2</v>
@@ -2457,46 +2445,46 @@
         <v>8</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C67" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" s="2">
         <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>74</v>
+        <v>201</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C68" s="4">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D68" s="4">
         <v>94</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>2</v>
@@ -2508,29 +2496,29 @@
         <v>12</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C70" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D70" s="2">
         <v>21</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>2</v>
@@ -2547,41 +2535,41 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C72" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D72" s="2">
         <v>18</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>206</v>
+        <v>62</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C73" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D73" s="2">
         <v>18</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>62</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>2</v>
@@ -2593,12 +2581,12 @@
         <v>9</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>2</v>
@@ -2610,15 +2598,15 @@
         <v>7</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C76" s="4">
         <v>11</v>
@@ -2627,12 +2615,12 @@
         <v>18</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>2</v>
@@ -2649,7 +2637,7 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>2</v>
@@ -2661,12 +2649,12 @@
         <v>7</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>2</v>
@@ -2678,12 +2666,12 @@
         <v>3</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>2</v>
@@ -2695,12 +2683,12 @@
         <v>1</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>2</v>
@@ -2712,12 +2700,12 @@
         <v>5</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>2</v>
@@ -2733,76 +2721,76 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C83" s="7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D83" s="7">
         <v>52</v>
       </c>
-      <c r="E83" s="6" t="s">
-        <v>50</v>
+      <c r="E83" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>44</v>
+        <v>189</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C84" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" s="4">
         <v>16</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C86" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="2">
         <v>4</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>2</v>
@@ -2814,12 +2802,12 @@
         <v>4</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>2</v>
@@ -2831,12 +2819,12 @@
         <v>3</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>2</v>
@@ -2848,15 +2836,15 @@
         <v>3</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>44</v>
+        <v>139</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C90" s="4">
         <v>11</v>
@@ -2865,12 +2853,12 @@
         <v>28</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>2</v>
@@ -2882,12 +2870,12 @@
         <v>1</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>2</v>
@@ -2904,7 +2892,7 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>2</v>
@@ -2916,12 +2904,12 @@
         <v>3</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>2</v>
@@ -2933,12 +2921,12 @@
         <v>6</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>2</v>
@@ -2950,12 +2938,12 @@
         <v>6</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>2</v>
@@ -2967,12 +2955,12 @@
         <v>2</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>2</v>
@@ -2984,29 +2972,29 @@
         <v>2</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C98" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D98" s="4">
         <v>8</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>161</v>
+        <v>77</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>2</v>
@@ -3014,16 +3002,14 @@
       <c r="C99" s="2">
         <v>1</v>
       </c>
-      <c r="D99" s="2">
-        <v>2</v>
-      </c>
+      <c r="D99" s="2"/>
       <c r="E99" s="1" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>2</v>
@@ -3032,83 +3018,83 @@
         <v>1</v>
       </c>
       <c r="D100" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="s">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C101" s="2">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2">
+        <v>3</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C102" s="2">
         <v>0</v>
       </c>
-      <c r="D101" s="2">
-        <v>2</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C102" s="7">
-        <v>118</v>
-      </c>
-      <c r="D102" s="7">
+      <c r="D102" s="2">
+        <v>2</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C103" s="7">
+        <v>124</v>
+      </c>
+      <c r="D103" s="7">
         <v>183</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C103" s="4">
-        <v>41</v>
-      </c>
-      <c r="D103" s="4">
+      <c r="E103" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C104" s="4">
+        <v>42</v>
+      </c>
+      <c r="D104" s="4">
         <v>72</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C104" s="2">
-        <v>2</v>
-      </c>
-      <c r="D104" s="2">
-        <v>6</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>15</v>
+      <c r="E104" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>2</v>
@@ -3117,542 +3103,540 @@
         <v>2</v>
       </c>
       <c r="D105" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C106" s="2">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D106" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C107" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D107" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="s">
-        <v>136</v>
+        <v>209</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C108" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D108" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="s">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C109" s="2">
+        <v>6</v>
+      </c>
+      <c r="D109" s="2">
+        <v>11</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="2">
         <v>10</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D110" s="2">
         <v>12</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C110" s="4">
-        <v>67</v>
-      </c>
-      <c r="D110" s="4">
+      <c r="E110" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C111" s="4">
+        <v>71</v>
+      </c>
+      <c r="D111" s="4">
         <v>90</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C111" s="2">
-        <v>2</v>
-      </c>
-      <c r="D111" s="2">
-        <v>3</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>153</v>
+      <c r="E111" s="3" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="s">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C112" s="2">
-        <v>6</v>
-      </c>
-      <c r="D112" s="2">
-        <v>9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D112" s="2"/>
       <c r="E112" s="1" t="s">
-        <v>153</v>
+        <v>35</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C113" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D113" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C114" s="2">
+        <v>7</v>
+      </c>
+      <c r="D114" s="2">
         <v>9</v>
       </c>
-      <c r="D114" s="2">
-        <v>10</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C115" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D115" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C116" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D116" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C117" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D117" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D118" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C119" s="4">
-        <v>10</v>
-      </c>
-      <c r="D119" s="4">
-        <v>21</v>
-      </c>
-      <c r="E119" s="3" t="s">
+      <c r="A119" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="2">
+        <v>2</v>
+      </c>
+      <c r="D119" s="2">
         <v>5</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C120" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D120" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C121" s="2">
-        <v>4</v>
-      </c>
-      <c r="D121" s="2">
-        <v>8</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>193</v>
+      <c r="A121" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C121" s="4">
+        <v>11</v>
+      </c>
+      <c r="D121" s="4">
+        <v>21</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D123" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C124" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C126" s="7">
-        <v>90</v>
-      </c>
-      <c r="D126" s="7">
+      <c r="A126" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>2</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2">
+        <v>1</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="7">
+        <v>98</v>
+      </c>
+      <c r="D128" s="7">
         <v>165</v>
       </c>
-      <c r="E126" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C127" s="4">
-        <v>17</v>
-      </c>
-      <c r="D127" s="4">
+      <c r="E128" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C129" s="4">
+        <v>20</v>
+      </c>
+      <c r="D129" s="4">
         <v>40</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C128" s="2">
-        <v>1</v>
-      </c>
-      <c r="D128" s="2">
-        <v>2</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C129" s="2">
-        <v>4</v>
-      </c>
-      <c r="D129" s="2">
-        <v>8</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>193</v>
+      <c r="E129" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="s">
-        <v>214</v>
+        <v>33</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C130" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D131" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C132" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D132" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C133" s="4">
-        <v>68</v>
-      </c>
-      <c r="D133" s="4">
-        <v>105</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>142</v>
+      <c r="A133" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2">
+        <v>6</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C134" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D134" s="2">
         <v>12</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C135" s="2">
-        <v>11</v>
-      </c>
-      <c r="D135" s="2">
-        <v>18</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>106</v>
+      <c r="A135" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C135" s="4">
+        <v>73</v>
+      </c>
+      <c r="D135" s="4">
+        <v>105</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C136" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D136" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>2</v>
@@ -3664,114 +3648,114 @@
         <v>18</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C138" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D138" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>195</v>
+        <v>25</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C139" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D139" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C140" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D140" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C141" s="4">
+      <c r="A141" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C141" s="2">
         <v>5</v>
       </c>
-      <c r="D141" s="4">
-        <v>20</v>
-      </c>
-      <c r="E141" s="3" t="s">
-        <v>161</v>
+      <c r="D141" s="2">
+        <v>13</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C142" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D142" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C143" s="2">
-        <v>2</v>
-      </c>
-      <c r="D143" s="2">
-        <v>7</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>23</v>
+      <c r="A143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C143" s="4">
+        <v>5</v>
+      </c>
+      <c r="D143" s="4">
+        <v>20</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>2</v>
@@ -3783,148 +3767,148 @@
         <v>3</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C145" s="2">
+        <v>2</v>
+      </c>
+      <c r="D145" s="2">
+        <v>7</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C146" s="2">
         <v>1</v>
       </c>
-      <c r="D145" s="2">
+      <c r="D146" s="2">
+        <v>3</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
         <v>4</v>
       </c>
-      <c r="E145" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C146" s="7">
-        <v>97</v>
-      </c>
-      <c r="D146" s="7">
+      <c r="E147" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C148" s="7">
+        <v>99</v>
+      </c>
+      <c r="D148" s="7">
         <v>168</v>
       </c>
-      <c r="E146" s="6" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C147" s="4">
-        <v>27</v>
-      </c>
-      <c r="D147" s="4">
+      <c r="E148" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" s="4">
+        <v>28</v>
+      </c>
+      <c r="D149" s="4">
         <v>56</v>
       </c>
-      <c r="E147" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C148" s="2">
-        <v>4</v>
-      </c>
-      <c r="D148" s="2">
-        <v>7</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C149" s="2">
-        <v>2</v>
-      </c>
-      <c r="D149" s="2">
-        <v>5</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>217</v>
+      <c r="E149" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C150" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D150" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C152" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D152" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>2</v>
@@ -3933,338 +3917,338 @@
         <v>1</v>
       </c>
       <c r="D153" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C154" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D154" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C155" s="4">
-        <v>62</v>
-      </c>
-      <c r="D155" s="4">
-        <v>96</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>24</v>
+      <c r="A155" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C155" s="2">
+        <v>1</v>
+      </c>
+      <c r="D155" s="2">
+        <v>5</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C156" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D156" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C157" s="2">
-        <v>17</v>
-      </c>
-      <c r="D157" s="2">
-        <v>19</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>184</v>
+      <c r="A157" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C157" s="4">
+        <v>63</v>
+      </c>
+      <c r="D157" s="4">
+        <v>96</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C159" s="2">
+        <v>17</v>
+      </c>
+      <c r="D159" s="2">
         <v>19</v>
       </c>
-      <c r="D159" s="2">
-        <v>25</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C160" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D160" s="2">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>138</v>
+        <v>40</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C161" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D161" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C162" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D162" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C163" s="4">
-        <v>8</v>
-      </c>
-      <c r="D163" s="4">
-        <v>16</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>193</v>
+      <c r="A163" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C163" s="2">
+        <v>2</v>
+      </c>
+      <c r="D163" s="2">
+        <v>5</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C164" s="2">
+        <v>1</v>
+      </c>
+      <c r="D164" s="2">
         <v>4</v>
       </c>
-      <c r="D164" s="2">
-        <v>7</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C165" s="2">
-        <v>1</v>
-      </c>
-      <c r="D165" s="2">
-        <v>3</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>15</v>
+      <c r="B165" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C165" s="4">
+        <v>8</v>
+      </c>
+      <c r="D165" s="4">
+        <v>16</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D166" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C167" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C168" s="2">
+        <v>1</v>
+      </c>
+      <c r="D168" s="2">
+        <v>3</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C169" s="2">
+        <v>2</v>
+      </c>
+      <c r="D169" s="2">
+        <v>2</v>
+      </c>
+      <c r="E169" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="6" t="s">
+    <row r="170">
+      <c r="A170" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C170" s="7">
+        <v>88</v>
+      </c>
+      <c r="D170" s="7">
+        <v>143</v>
+      </c>
+      <c r="E170" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B168" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C168" s="7">
-        <v>86</v>
-      </c>
-      <c r="D168" s="7">
-        <v>143</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C169" s="4">
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C171" s="4">
         <v>14</v>
       </c>
-      <c r="D169" s="4">
+      <c r="D171" s="4">
         <v>32</v>
       </c>
-      <c r="E169" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C170" s="2">
-        <v>1</v>
-      </c>
-      <c r="D170" s="2">
-        <v>2</v>
-      </c>
-      <c r="E170" s="1" t="s">
+      <c r="E171" s="3" t="s">
         <v>193</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C171" s="2">
-        <v>1</v>
-      </c>
-      <c r="D171" s="2">
-        <v>1</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>2</v>
@@ -4273,355 +4257,355 @@
         <v>1</v>
       </c>
       <c r="D173" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C174" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D174" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C175" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D175" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>217</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C176" s="2">
+        <v>4</v>
+      </c>
+      <c r="D176" s="2">
+        <v>8</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C177" s="2">
+        <v>2</v>
+      </c>
+      <c r="D177" s="2">
         <v>5</v>
       </c>
-      <c r="D176" s="2">
-        <v>7</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C177" s="4">
-        <v>70</v>
-      </c>
-      <c r="D177" s="4">
-        <v>102</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>185</v>
+      <c r="E177" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C178" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D178" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C179" s="2">
-        <v>9</v>
-      </c>
-      <c r="D179" s="2">
-        <v>17</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>143</v>
+      <c r="A179" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C179" s="4">
+        <v>72</v>
+      </c>
+      <c r="D179" s="4">
+        <v>102</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C180" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D180" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>209</v>
+        <v>167</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C181" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D181" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C182" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D182" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C183" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D183" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C184" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D184" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>36</v>
+        <v>140</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B185" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C185" s="4">
-        <v>2</v>
-      </c>
-      <c r="D185" s="4">
+      <c r="A185" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C185" s="2">
         <v>9</v>
       </c>
-      <c r="E185" s="3" t="s">
-        <v>109</v>
+      <c r="D185" s="2">
+        <v>10</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C186" s="2">
+        <v>4</v>
+      </c>
+      <c r="D186" s="2">
+        <v>7</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C187" s="4">
+        <v>2</v>
+      </c>
+      <c r="D187" s="4">
+        <v>9</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C188" s="2">
         <v>1</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D188" s="2">
         <v>3</v>
       </c>
-      <c r="E186" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C187" s="2">
+      <c r="E188" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C189" s="2">
         <v>1</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D189" s="2">
         <v>3</v>
       </c>
-      <c r="E187" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C188" s="7">
+      <c r="E189" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D188" s="7">
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" s="7">
+        <v>18</v>
+      </c>
+      <c r="D190" s="7">
         <v>47</v>
       </c>
-      <c r="E188" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C189" s="4">
+      <c r="E190" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C191" s="4">
         <v>5</v>
       </c>
-      <c r="D189" s="4">
+      <c r="D191" s="4">
         <v>17</v>
       </c>
-      <c r="E189" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C190" s="2">
-        <v>1</v>
-      </c>
-      <c r="D190" s="2">
-        <v>4</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C191" s="2">
-        <v>2</v>
-      </c>
-      <c r="D191" s="2">
-        <v>4</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>193</v>
+      <c r="E191" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C192" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D192" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C193" s="4">
-        <v>10</v>
-      </c>
-      <c r="D193" s="4">
-        <v>24</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>51</v>
+      <c r="A193" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C193" s="2">
+        <v>2</v>
+      </c>
+      <c r="D193" s="2">
+        <v>4</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>2</v>
@@ -4630,219 +4614,217 @@
         <v>2</v>
       </c>
       <c r="D194" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B195" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C195" s="2">
-        <v>3</v>
-      </c>
-      <c r="D195" s="2">
-        <v>4</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>74</v>
+      <c r="A195" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C195" s="4">
+        <v>10</v>
+      </c>
+      <c r="D195" s="4">
+        <v>24</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C196" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D196" s="2">
         <v>4</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C197" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D197" s="2">
         <v>4</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>193</v>
+        <v>73</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C198" s="4">
-        <v>1</v>
-      </c>
-      <c r="D198" s="4">
-        <v>6</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>21</v>
+      <c r="A198" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C198" s="2">
+        <v>3</v>
+      </c>
+      <c r="D198" s="2">
+        <v>4</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C199" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D199" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B200" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C200" s="2">
-        <v>0</v>
-      </c>
-      <c r="D200" s="2">
-        <v>1</v>
-      </c>
-      <c r="E200" s="1" t="s">
-        <v>33</v>
+      <c r="A200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C200" s="4">
+        <v>3</v>
+      </c>
+      <c r="D200" s="4">
+        <v>6</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D201" s="2">
         <v>1</v>
       </c>
       <c r="E201" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C202" s="2">
+        <v>1</v>
+      </c>
+      <c r="D202" s="2">
+        <v>1</v>
+      </c>
+      <c r="E202" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C202" s="7">
-        <v>83</v>
-      </c>
-      <c r="D202" s="7">
+    <row r="203">
+      <c r="A203" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C203" s="2">
+        <v>2</v>
+      </c>
+      <c r="D203" s="2"/>
+      <c r="E203" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C204" s="7">
+        <v>86</v>
+      </c>
+      <c r="D204" s="7">
         <v>129</v>
       </c>
-      <c r="E202" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B203" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C203" s="4">
+      <c r="E204" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C205" s="4">
         <v>30</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D205" s="4">
         <v>43</v>
       </c>
-      <c r="E203" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C204" s="2">
-        <v>3</v>
-      </c>
-      <c r="D204" s="2">
-        <v>6</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B205" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C205" s="2">
-        <v>1</v>
-      </c>
-      <c r="D205" s="2">
-        <v>3</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>15</v>
+      <c r="E205" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C206" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>155</v>
+        <v>190</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>2</v>
@@ -4851,49 +4833,49 @@
         <v>1</v>
       </c>
       <c r="D207" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>193</v>
+        <v>16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C208" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D208" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C209" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D209" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>2</v>
@@ -4902,627 +4884,627 @@
         <v>8</v>
       </c>
       <c r="D210" s="2">
+        <v>10</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C211" s="2">
+        <v>5</v>
+      </c>
+      <c r="D211" s="2">
         <v>7</v>
       </c>
-      <c r="E210" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B211" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C211" s="4">
-        <v>41</v>
-      </c>
-      <c r="D211" s="4">
-        <v>70</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>198</v>
+      <c r="E211" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C212" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D212" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>15</v>
+        <v>143</v>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B213" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C213" s="2">
-        <v>4</v>
-      </c>
-      <c r="D213" s="2">
-        <v>7</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>36</v>
+      <c r="A213" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C213" s="4">
+        <v>44</v>
+      </c>
+      <c r="D213" s="4">
+        <v>70</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C214" s="2">
+        <v>1</v>
+      </c>
+      <c r="D214" s="2">
+        <v>3</v>
+      </c>
+      <c r="E214" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C214" s="2">
-        <v>6</v>
-      </c>
-      <c r="D214" s="2">
-        <v>10</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C215" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D215" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>182</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C216" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D216" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C217" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D217" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C218" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D218" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C219" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D219" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B220" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C220" s="4">
-        <v>12</v>
-      </c>
-      <c r="D220" s="4">
-        <v>16</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>74</v>
+      <c r="A220" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C220" s="2">
+        <v>2</v>
+      </c>
+      <c r="D220" s="2">
+        <v>4</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C221" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D221" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="s">
+      <c r="A222" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C222" s="2">
-        <v>1</v>
-      </c>
-      <c r="D222" s="2">
-        <v>2</v>
-      </c>
-      <c r="E222" s="1" t="s">
-        <v>193</v>
+      <c r="B222" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C222" s="4">
+        <v>12</v>
+      </c>
+      <c r="D222" s="4">
+        <v>16</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C223" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D223" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C224" s="2">
+        <v>1</v>
+      </c>
+      <c r="D224" s="2">
+        <v>2</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C225" s="2">
+        <v>2</v>
+      </c>
+      <c r="D225" s="2">
         <v>3</v>
       </c>
-      <c r="D224" s="2">
-        <v>2</v>
-      </c>
-      <c r="E224" s="1" t="s">
+      <c r="E225" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C226" s="2">
+        <v>3</v>
+      </c>
+      <c r="D226" s="2">
+        <v>2</v>
+      </c>
+      <c r="E226" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C225" s="7">
-        <v>96</v>
-      </c>
-      <c r="D225" s="7">
+    <row r="227">
+      <c r="A227" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C227" s="7">
+        <v>102</v>
+      </c>
+      <c r="D227" s="7">
         <v>168</v>
       </c>
-      <c r="E225" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B226" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C226" s="4">
-        <v>24</v>
-      </c>
-      <c r="D226" s="4">
+      <c r="E227" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C228" s="4">
+        <v>25</v>
+      </c>
+      <c r="D228" s="4">
         <v>48</v>
       </c>
-      <c r="E226" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C227" s="2">
-        <v>2</v>
-      </c>
-      <c r="D227" s="2">
-        <v>4</v>
-      </c>
-      <c r="E227" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C228" s="2">
-        <v>2</v>
-      </c>
-      <c r="D228" s="2">
-        <v>5</v>
-      </c>
-      <c r="E228" s="1" t="s">
-        <v>217</v>
+      <c r="E228" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C229" s="2">
+        <v>3</v>
+      </c>
+      <c r="D229" s="2">
         <v>4</v>
       </c>
-      <c r="D229" s="2">
-        <v>15</v>
-      </c>
       <c r="E229" s="1" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="s">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C230" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D230" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>162</v>
+        <v>211</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="s">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C231" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D231" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C232" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D232" s="2">
         <v>10</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B233" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C233" s="4">
-        <v>57</v>
-      </c>
-      <c r="D233" s="4">
-        <v>98</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>199</v>
+      <c r="A233" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C233" s="2">
+        <v>5</v>
+      </c>
+      <c r="D233" s="2">
+        <v>7</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C234" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D234" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>91</v>
+        <v>211</v>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B235" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C235" s="2">
-        <v>7</v>
-      </c>
-      <c r="D235" s="2">
-        <v>13</v>
-      </c>
-      <c r="E235" s="1" t="s">
-        <v>171</v>
+      <c r="A235" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C235" s="4">
+        <v>62</v>
+      </c>
+      <c r="D235" s="4">
+        <v>98</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C236" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D236" s="2">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B237" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C237" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D237" s="2">
         <v>13</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B238" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C238" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D238" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C239" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D239" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>182</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C240" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D240" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C241" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D241" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>37</v>
+        <v>180</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B242" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C242" s="4">
-        <v>15</v>
-      </c>
-      <c r="D242" s="4">
-        <v>22</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>172</v>
+      <c r="A242" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C242" s="2">
+        <v>9</v>
+      </c>
+      <c r="D242" s="2">
+        <v>11</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C243" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D243" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="s">
+      <c r="A244" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B244" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C244" s="2">
-        <v>1</v>
-      </c>
-      <c r="D244" s="2">
-        <v>3</v>
-      </c>
-      <c r="E244" s="1" t="s">
+      <c r="B244" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C244" s="4">
         <v>15</v>
+      </c>
+      <c r="D244" s="4">
+        <v>22</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="s">
-        <v>165</v>
+        <v>74</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C245" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D245" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="s">
-        <v>163</v>
+        <v>19</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C246" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D246" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>111</v>
+        <v>16</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>2</v>
@@ -5531,134 +5513,134 @@
         <v>1</v>
       </c>
       <c r="D247" s="2">
+        <v>3</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C248" s="2">
+        <v>7</v>
+      </c>
+      <c r="D248" s="2">
+        <v>6</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C249" s="2">
         <v>1</v>
       </c>
-      <c r="E247" s="1" t="s">
+      <c r="D249" s="2">
+        <v>1</v>
+      </c>
+      <c r="E249" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="6" t="s">
+    <row r="250">
+      <c r="A250" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B248" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C248" s="7">
-        <v>106</v>
-      </c>
-      <c r="D248" s="7">
+      <c r="B250" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C250" s="7">
+        <v>118</v>
+      </c>
+      <c r="D250" s="7">
         <v>175</v>
       </c>
-      <c r="E248" s="6" t="s">
+      <c r="E250" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B249" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C249" s="4">
-        <v>38</v>
-      </c>
-      <c r="D249" s="4">
+    <row r="251">
+      <c r="A251" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C251" s="4">
+        <v>39</v>
+      </c>
+      <c r="D251" s="4">
         <v>53</v>
       </c>
-      <c r="E249" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C250" s="2">
-        <v>4</v>
-      </c>
-      <c r="D250" s="2">
-        <v>10</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C251" s="2">
-        <v>3</v>
-      </c>
-      <c r="D251" s="2">
-        <v>3</v>
-      </c>
-      <c r="E251" s="1" t="s">
-        <v>91</v>
+      <c r="E251" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C252" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D252" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C253" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D253" s="2">
         <v>3</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="s">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C254" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D254" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>2</v>
@@ -5667,316 +5649,365 @@
         <v>2</v>
       </c>
       <c r="D255" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C256" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D256" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>66</v>
+        <v>151</v>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C257" s="4">
-        <v>47</v>
-      </c>
-      <c r="D257" s="4">
-        <v>81</v>
-      </c>
-      <c r="E257" s="3" t="s">
-        <v>69</v>
+      <c r="A257" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C257" s="2">
+        <v>2</v>
+      </c>
+      <c r="D257" s="2">
+        <v>4</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B258" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C258" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D258" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C259" s="2">
-        <v>5</v>
-      </c>
-      <c r="D259" s="2">
-        <v>10</v>
-      </c>
-      <c r="E259" s="1" t="s">
-        <v>193</v>
+      <c r="A259" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C259" s="4">
+        <v>54</v>
+      </c>
+      <c r="D259" s="4">
+        <v>81</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C260" s="2">
-        <v>10</v>
-      </c>
-      <c r="D260" s="2">
-        <v>16</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D260" s="2"/>
       <c r="E260" s="1" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C261" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D261" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="s">
-        <v>194</v>
+        <v>15</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C262" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D262" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C263" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D263" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C264" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D264" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="s">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C265" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D265" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C266" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D266" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B267" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C267" s="4">
-        <v>21</v>
-      </c>
-      <c r="D267" s="4">
-        <v>41</v>
-      </c>
-      <c r="E267" s="3" t="s">
-        <v>70</v>
+      <c r="A267" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C267" s="2">
+        <v>12</v>
+      </c>
+      <c r="D267" s="2">
+        <v>15</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C268" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D268" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>15</v>
+        <v>180</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C269" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D269" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>36</v>
+        <v>190</v>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="s">
+      <c r="A270" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B270" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C270" s="2">
-        <v>2</v>
-      </c>
-      <c r="D270" s="2">
-        <v>6</v>
-      </c>
-      <c r="E270" s="1" t="s">
-        <v>15</v>
+      <c r="B270" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C270" s="4">
+        <v>25</v>
+      </c>
+      <c r="D270" s="4">
+        <v>41</v>
+      </c>
+      <c r="E270" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C271" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D271" s="2">
         <v>6</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C272" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D272" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>153</v>
+        <v>38</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C273" s="2">
+        <v>3</v>
+      </c>
+      <c r="D273" s="2">
+        <v>6</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C274" s="2">
+        <v>3</v>
+      </c>
+      <c r="D274" s="2">
+        <v>6</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C275" s="2">
+        <v>7</v>
+      </c>
+      <c r="D275" s="2">
+        <v>9</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C276" s="2">
         <v>1</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D276" s="2">
         <v>4</v>
       </c>
-      <c r="E273" s="1" t="s">
-        <v>161</v>
+      <c r="E276" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5996,30 +6027,30 @@
     <hyperlink ref="B84" r:id="rId13" display="Full Product List"/>
     <hyperlink ref="B90" r:id="rId14" display="Full Product List"/>
     <hyperlink ref="B98" r:id="rId15" display="Full Product List"/>
-    <hyperlink ref="B103" r:id="rId16" display="Full Product List"/>
-    <hyperlink ref="B110" r:id="rId17" display="Full Product List"/>
-    <hyperlink ref="B119" r:id="rId18" display="Full Product List"/>
-    <hyperlink ref="B127" r:id="rId19" display="Full Product List"/>
-    <hyperlink ref="B133" r:id="rId20" display="Full Product List"/>
-    <hyperlink ref="B141" r:id="rId21" display="Full Product List"/>
-    <hyperlink ref="B147" r:id="rId22" display="Full Product List"/>
-    <hyperlink ref="B155" r:id="rId23" display="Full Product List"/>
-    <hyperlink ref="B163" r:id="rId24" display="Full Product List"/>
-    <hyperlink ref="B169" r:id="rId25" display="Full Product List"/>
-    <hyperlink ref="B177" r:id="rId26" display="Full Product List"/>
-    <hyperlink ref="B185" r:id="rId27" display="Full Product List"/>
-    <hyperlink ref="B189" r:id="rId28" display="Full Product List"/>
-    <hyperlink ref="B193" r:id="rId29" display="Full Product List"/>
-    <hyperlink ref="B198" r:id="rId30" display="Full Product List"/>
-    <hyperlink ref="B203" r:id="rId31" display="Full Product List"/>
-    <hyperlink ref="B211" r:id="rId32" display="Full Product List"/>
-    <hyperlink ref="B220" r:id="rId33" display="Full Product List"/>
-    <hyperlink ref="B226" r:id="rId34" display="Full Product List"/>
-    <hyperlink ref="B233" r:id="rId35" display="Full Product List"/>
-    <hyperlink ref="B242" r:id="rId36" display="Full Product List"/>
-    <hyperlink ref="B249" r:id="rId37" display="Full Product List"/>
-    <hyperlink ref="B257" r:id="rId38" display="Full Product List"/>
-    <hyperlink ref="B267" r:id="rId39" display="Full Product List"/>
+    <hyperlink ref="B104" r:id="rId16" display="Full Product List"/>
+    <hyperlink ref="B111" r:id="rId17" display="Full Product List"/>
+    <hyperlink ref="B121" r:id="rId18" display="Full Product List"/>
+    <hyperlink ref="B129" r:id="rId19" display="Full Product List"/>
+    <hyperlink ref="B135" r:id="rId20" display="Full Product List"/>
+    <hyperlink ref="B143" r:id="rId21" display="Full Product List"/>
+    <hyperlink ref="B149" r:id="rId22" display="Full Product List"/>
+    <hyperlink ref="B157" r:id="rId23" display="Full Product List"/>
+    <hyperlink ref="B165" r:id="rId24" display="Full Product List"/>
+    <hyperlink ref="B171" r:id="rId25" display="Full Product List"/>
+    <hyperlink ref="B179" r:id="rId26" display="Full Product List"/>
+    <hyperlink ref="B187" r:id="rId27" display="Full Product List"/>
+    <hyperlink ref="B191" r:id="rId28" display="Full Product List"/>
+    <hyperlink ref="B195" r:id="rId29" display="Full Product List"/>
+    <hyperlink ref="B200" r:id="rId30" display="Full Product List"/>
+    <hyperlink ref="B205" r:id="rId31" display="Full Product List"/>
+    <hyperlink ref="B213" r:id="rId32" display="Full Product List"/>
+    <hyperlink ref="B222" r:id="rId33" display="Full Product List"/>
+    <hyperlink ref="B228" r:id="rId34" display="Full Product List"/>
+    <hyperlink ref="B235" r:id="rId35" display="Full Product List"/>
+    <hyperlink ref="B244" r:id="rId36" display="Full Product List"/>
+    <hyperlink ref="B251" r:id="rId37" display="Full Product List"/>
+    <hyperlink ref="B259" r:id="rId38" display="Full Product List"/>
+    <hyperlink ref="B270" r:id="rId39" display="Full Product List"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6032,38 +6063,38 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="16">
-        <v>46311.40416666667</v>
+        <v>46316.438888888886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="16"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>128</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -6071,7 +6102,7 @@
         <v>26632319</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" s="8">
         <v>26.09</v>
@@ -6079,18 +6110,18 @@
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="8">
@@ -6102,7 +6133,7 @@
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8">
@@ -6111,34 +6142,34 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="10" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="10" t="s">
@@ -6147,20 +6178,20 @@
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16">
@@ -6169,61 +6200,61 @@
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6232,66 +6263,66 @@
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="14" t="s">
-        <v>115</v>
+      <c r="C24" s="15" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="10" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="12">
@@ -6300,16 +6331,16 @@
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="10" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="10" t="s">
@@ -6318,53 +6349,53 @@
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="10"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="10"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="10"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="12">
@@ -6373,14 +6404,14 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="10"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="16">
@@ -6389,7 +6420,7 @@
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="16">
@@ -6398,49 +6429,49 @@
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="16"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="16"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="10"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="10"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="10"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="10"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="10"/>
@@ -6454,35 +6485,35 @@
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="10"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="10"/>
@@ -6496,84 +6527,84 @@
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" s="8"/>
-      <c r="C57" s="14"/>
+      <c r="C57" s="15"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B60" s="8"/>
       <c r="C60" s="8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="10"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="10"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="12"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="12"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="12"/>
     </row>
     <row r="67">
       <c r="A67" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
       <c r="E67" s="8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
